--- a/rules/CORE-000361/negative/02/data/unit-test-coreid-CG0035-negative-2.xlsx
+++ b/rules/CORE-000361/negative/02/data/unit-test-coreid-CG0035-negative-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JanakiRaman\CORE\Rule_Authoring\core-contributor\rules\CORE-000361\negative\02\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8705B9-24B3-4E28-AF47-CA4D998F3B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2932AC2-CD9C-423C-9316-B3FDD86A9ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2445" uniqueCount="475">
   <si>
     <t>Product</t>
   </si>
@@ -1469,45 +1469,6 @@
   </si>
   <si>
     <t>Vital Signs</t>
-  </si>
-  <si>
-    <t>800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 </t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>1500</t>
-  </si>
-  <si>
-    <t>12</t>
   </si>
 </sst>
 </file>
@@ -1593,7 +1554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1621,7 +1582,18 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2032,8 +2004,8 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
-        <v>476</v>
+      <c r="A2" s="12">
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>471</v>
@@ -2041,19 +2013,19 @@
       <c r="C2" t="s">
         <v>166</v>
       </c>
-      <c r="D2" t="s">
-        <v>484</v>
+      <c r="D2" s="12">
+        <v>18</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
-        <v>468</v>
+      <c r="F2" s="13">
+        <v>1400</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
-        <v>476</v>
+      <c r="A3" s="12">
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>471</v>
@@ -2061,19 +2033,19 @@
       <c r="C3" t="s">
         <v>166</v>
       </c>
-      <c r="D3" t="s">
-        <v>484</v>
+      <c r="D3" s="12">
+        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="14" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
-        <v>477</v>
+      <c r="A4" s="12">
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>471</v>
@@ -2081,19 +2053,19 @@
       <c r="C4" t="s">
         <v>166</v>
       </c>
-      <c r="D4" t="s">
-        <v>485</v>
+      <c r="D4" s="12">
+        <v>19</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" t="s">
-        <v>486</v>
+      <c r="F4" s="13">
+        <v>1500</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
-        <v>477</v>
+      <c r="A5" s="12">
+        <v>2</v>
       </c>
       <c r="B5" t="s">
         <v>471</v>
@@ -2101,19 +2073,19 @@
       <c r="C5" t="s">
         <v>166</v>
       </c>
-      <c r="D5" t="s">
-        <v>485</v>
+      <c r="D5" s="12">
+        <v>19</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="14" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>478</v>
+      <c r="A6" s="12">
+        <v>3</v>
       </c>
       <c r="B6" t="s">
         <v>471</v>
@@ -2121,19 +2093,19 @@
       <c r="C6" t="s">
         <v>166</v>
       </c>
-      <c r="D6" t="s">
-        <v>301</v>
+      <c r="D6" s="12">
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
-      <c r="F6" t="s">
-        <v>468</v>
+      <c r="F6" s="13">
+        <v>1400</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
-        <v>478</v>
+      <c r="A7" s="12">
+        <v>3</v>
       </c>
       <c r="B7" t="s">
         <v>471</v>
@@ -2141,21 +2113,21 @@
       <c r="C7" t="s">
         <v>166</v>
       </c>
-      <c r="D7" t="s">
-        <v>301</v>
+      <c r="D7" s="12">
+        <v>48</v>
       </c>
       <c r="E7" t="s">
         <v>20</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="14" t="s">
         <v>69</v>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>479</v>
+      <c r="A8" s="12">
+        <v>4</v>
       </c>
       <c r="B8" t="s">
         <v>471</v>
@@ -2163,21 +2135,21 @@
       <c r="C8" t="s">
         <v>166</v>
       </c>
-      <c r="D8" t="s">
-        <v>450</v>
+      <c r="D8" s="12">
+        <v>49</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
       </c>
-      <c r="F8" t="s">
-        <v>486</v>
+      <c r="F8" s="13">
+        <v>1500</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
-        <v>479</v>
+      <c r="A9" s="12">
+        <v>4</v>
       </c>
       <c r="B9" t="s">
         <v>471</v>
@@ -2185,19 +2157,19 @@
       <c r="C9" t="s">
         <v>166</v>
       </c>
-      <c r="D9" t="s">
-        <v>450</v>
+      <c r="D9" s="12">
+        <v>49</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="14" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
-        <v>480</v>
+      <c r="A10" s="12">
+        <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>472</v>
@@ -2205,19 +2177,19 @@
       <c r="C10" t="s">
         <v>166</v>
       </c>
-      <c r="D10" t="s">
-        <v>487</v>
+      <c r="D10" s="12">
+        <v>12</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
       </c>
-      <c r="F10" t="s">
-        <v>475</v>
+      <c r="F10" s="13">
+        <v>800</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>480</v>
+      <c r="A11" s="12">
+        <v>5</v>
       </c>
       <c r="B11" t="s">
         <v>472</v>
@@ -2225,19 +2197,19 @@
       <c r="C11" t="s">
         <v>166</v>
       </c>
-      <c r="D11" t="s">
-        <v>487</v>
+      <c r="D11" s="12">
+        <v>12</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="14" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>481</v>
+      <c r="A12" s="12">
+        <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>472</v>
@@ -2245,19 +2217,19 @@
       <c r="C12" t="s">
         <v>166</v>
       </c>
-      <c r="D12" t="s">
-        <v>484</v>
+      <c r="D12" s="12">
+        <v>18</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
-      <c r="F12" t="s">
-        <v>468</v>
+      <c r="F12" s="13">
+        <v>1400</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
-        <v>481</v>
+      <c r="A13" s="12">
+        <v>6</v>
       </c>
       <c r="B13" t="s">
         <v>472</v>
@@ -2265,19 +2237,19 @@
       <c r="C13" t="s">
         <v>166</v>
       </c>
-      <c r="D13" t="s">
-        <v>484</v>
+      <c r="D13" s="12">
+        <v>18</v>
       </c>
       <c r="E13" t="s">
         <v>20</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="14" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
-        <v>482</v>
+      <c r="A14" s="12">
+        <v>7</v>
       </c>
       <c r="B14" t="s">
         <v>472</v>
@@ -2285,19 +2257,19 @@
       <c r="C14" t="s">
         <v>166</v>
       </c>
-      <c r="D14" t="s">
-        <v>369</v>
+      <c r="D14" s="12">
+        <v>41</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
       </c>
-      <c r="F14" t="s">
-        <v>475</v>
+      <c r="F14" s="13">
+        <v>800</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
-        <v>482</v>
+      <c r="A15" s="12">
+        <v>7</v>
       </c>
       <c r="B15" t="s">
         <v>472</v>
@@ -2305,19 +2277,19 @@
       <c r="C15" t="s">
         <v>166</v>
       </c>
-      <c r="D15" t="s">
-        <v>369</v>
+      <c r="D15" s="12">
+        <v>41</v>
       </c>
       <c r="E15" t="s">
         <v>20</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="14" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
-        <v>483</v>
+      <c r="A16" s="12">
+        <v>8</v>
       </c>
       <c r="B16" t="s">
         <v>472</v>
@@ -2325,19 +2297,19 @@
       <c r="C16" t="s">
         <v>166</v>
       </c>
-      <c r="D16" t="s">
-        <v>375</v>
+      <c r="D16" s="12">
+        <v>47</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
       </c>
-      <c r="F16" t="s">
-        <v>468</v>
+      <c r="F16" s="13">
+        <v>1400</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
-        <v>483</v>
+      <c r="A17" s="12">
+        <v>8</v>
       </c>
       <c r="B17" t="s">
         <v>472</v>
@@ -2345,13 +2317,13 @@
       <c r="C17" t="s">
         <v>166</v>
       </c>
-      <c r="D17" t="s">
-        <v>375</v>
+      <c r="D17" s="12">
+        <v>47</v>
       </c>
       <c r="E17" t="s">
         <v>20</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="14" t="s">
         <v>467</v>
       </c>
     </row>
@@ -5424,10 +5396,10 @@
       <c r="R19" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="S19" s="7">
+      <c r="S19" s="8">
         <v>1500</v>
       </c>
-      <c r="T19" s="7" t="s">
+      <c r="T19" s="8" t="s">
         <v>71</v>
       </c>
       <c r="U19" s="7" t="s">
@@ -7417,10 +7389,10 @@
       <c r="R48" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="S48" s="7">
+      <c r="S48" s="8">
         <v>1400</v>
       </c>
-      <c r="T48" s="7" t="s">
+      <c r="T48" s="8" t="s">
         <v>69</v>
       </c>
       <c r="U48" s="7" t="s">
@@ -8484,6 +8456,7 @@
   <cols>
     <col min="1" max="1" width="15.6328125" customWidth="1"/>
     <col min="3" max="3" width="19.1796875" customWidth="1"/>
+    <col min="17" max="17" width="13.36328125" customWidth="1"/>
     <col min="18" max="18" width="21.36328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9518,10 +9491,10 @@
       <c r="P18" s="7">
         <v>2</v>
       </c>
-      <c r="Q18" s="7" t="s">
+      <c r="Q18" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="R18" s="7" t="s">
+      <c r="R18" s="8" t="s">
         <v>69</v>
       </c>
       <c r="S18" s="7" t="s">
@@ -10806,10 +10779,10 @@
       <c r="P41" s="7">
         <v>2</v>
       </c>
-      <c r="Q41" s="7">
+      <c r="Q41" s="8">
         <v>800</v>
       </c>
-      <c r="R41" s="7" t="s">
+      <c r="R41" s="8" t="s">
         <v>57</v>
       </c>
       <c r="S41" s="7" t="s">
@@ -12012,6 +11985,7 @@
   <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="19.08984375" customWidth="1"/>
     <col min="3" max="3" width="13.7265625" customWidth="1"/>
     <col min="4" max="4" width="18.6328125" customWidth="1"/>
     <col min="5" max="5" width="19.90625" customWidth="1"/>
@@ -12266,15 +12240,15 @@
         <v>143</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>475</v>
+      <c r="C12" s="11">
+        <v>800</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>57</v>
